--- a/accountant-skill/data/Jan2026/cash_payments_journal.xlsx
+++ b/accountant-skill/data/Jan2026/cash_payments_journal.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cash Payments Journal" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Payments Journal" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>320000</v>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5200</v>
+        <v>65000</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>450000</v>
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>5200</v>
+        <v>65000</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>380000</v>
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5200</v>
+        <v>65000</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>350000</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>5210</v>
+        <v>63000</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>125000</v>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>185000</v>
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>5220</v>
+        <v>65000</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>55000</v>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>95000</v>
@@ -882,10 +882,10 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5500</v>
+        <v>64000</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>85000</v>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1030</v>
+        <v>10000</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>100000</v>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>198000</v>
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>5700</v>
+        <v>65000</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>65000</v>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>5400</v>
+        <v>65000</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>95000</v>
@@ -1104,10 +1104,10 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>5600</v>
+        <v>60000</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>120000</v>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3020</v>
+        <v>30200</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>200000</v>
